--- a/plantillas/101.xlsx
+++ b/plantillas/101.xlsx
@@ -58,13 +58,13 @@
     <definedName name="MARCA_44">Listas!$AU$2:$AU$2</definedName>
     <definedName name="MARCA_45">Listas!$AV$2:$AV$36</definedName>
     <definedName name="MARCA_46">Listas!$AW$2:$AW$26</definedName>
-    <definedName name="MARCA_47">Listas!$AX$2:$AX$6</definedName>
+    <definedName name="MARCA_47">Listas!$AX$2:$AX$7</definedName>
     <definedName name="MARCA_48">Listas!$AY$2:$AY$58</definedName>
     <definedName name="MARCA_49">Listas!$AZ$2:$AZ$10</definedName>
     <definedName name="MARCA_50">Listas!$BA$2:$BA$11</definedName>
     <definedName name="MARCA_51">Listas!$BB$2:$BB$12</definedName>
     <definedName name="MARCA_52">Listas!$BC$2:$BC$54</definedName>
-    <definedName name="MARCA_53">Listas!$BD$2:$BD$7</definedName>
+    <definedName name="MARCA_53">Listas!$BD$2:$BD$6</definedName>
     <definedName name="MARCA_54">Listas!$BE$2:$BE$2</definedName>
     <definedName name="MARCA_55">Listas!$BF$2:$BF$12</definedName>
     <definedName name="MARCA_56">Listas!$BG$2:$BG$2</definedName>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA DE HIGADO 1 · 93513070000</t>
+          <t>UC SNACK BARRA RELLENA DE POLLO 1UD · 93513080000</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA DE POLLO 1UD · 93513080000</t>
+          <t>UC SNACK BARRA RELLENA M/MANI 1UD · 93513050000</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA M/MANI 1UD · 93513050000</t>
+          <t>UC SNACK BARRA RELLENA POLLO 8UD · 93514990000</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA POLLO 8UD · 93514990000</t>
+          <t>UC SNACK V BARRA RELLENA HIGADO 8UD · 93514980000</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>PRO PET 4KG CACHORRO · 93500000400</t>
+          <t>PRO PET 4KG ADULTO · 93500000300</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>UC SNACK V BARRA RELLENA HIGADO 8UD · 93514980000</t>
+          <t>UC SNACK V BARRA RELLENA M MANI 8UD · 93514960000</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -10293,6 +10293,11 @@
           <t>SD CANINE U/D DRY 8.5LB · 90304020000</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>PRO PET 4KG CACHORRO · 93500000400</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>PP CACHORRO RZ GRANDE 3.5KG · 93501121000</t>
@@ -10316,11 +10321,6 @@
       <c r="BC7" t="inlineStr">
         <is>
           <t>ROYAL CAN BHN SHITZU ADULTO 1.5 KG. · 90401980000</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>UC SNACK V BARRA RELLENA M MANI 8UD · 93514960000</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -22019,7 +22019,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         </is>
       </c>
       <c r="C595" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         </is>
       </c>
       <c r="C614" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         </is>
       </c>
       <c r="C630" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -26730,16 +26730,16 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>PRO PET 4KG CACHORRO · 93500000400</t>
+          <t>PRO PET 4KG ADULTO · 93500000300</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>93500000400</t>
+          <t>93500000300</t>
         </is>
       </c>
       <c r="C634" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -26750,36 +26750,36 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
+          <t>PRO PET 4KG CACHORRO · 93500000400</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>90009660000</t>
+          <t>93500000400</t>
         </is>
       </c>
       <c r="C635" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PRO PET</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
+          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>90009650000</t>
+          <t>90009660000</t>
         </is>
       </c>
       <c r="C636" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -26790,16 +26790,16 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>PP ADULTO RZ PEQUENA OPTI 7.5KG · 93501251000</t>
+          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>93501251000</t>
+          <t>90009650000</t>
         </is>
       </c>
       <c r="C637" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -26810,16 +26810,16 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
+          <t>PP ADULTO RZ PEQUENA OPTI 7.5KG · 93501251000</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>93510171000</t>
+          <t>93501251000</t>
         </is>
       </c>
       <c r="C638" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -26830,16 +26830,16 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  MD/G 13KG · 93510181000</t>
+          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>93510181000</t>
+          <t>93510171000</t>
         </is>
       </c>
       <c r="C639" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -26850,16 +26850,16 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>PP CACHORRO RZ GRANDE 3.5KG · 93501121000</t>
+          <t>PP ADULTO SENSITIVE SKIN  MD/G 13KG · 93510181000</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>93501121000</t>
+          <t>93510181000</t>
         </is>
       </c>
       <c r="C640" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -26870,16 +26870,16 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>PP GATO ADULTO SALMON 85G · 90403691000</t>
+          <t>PP CACHORRO RZ GRANDE 3.5KG · 93501121000</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>90403691000</t>
+          <t>93501121000</t>
         </is>
       </c>
       <c r="C641" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -26890,16 +26890,16 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
+          <t>PP GATO ADULTO SALMON 85G · 90403691000</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>90401421000</t>
+          <t>90403691000</t>
         </is>
       </c>
       <c r="C642" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -26910,16 +26910,16 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
+          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>93519420000</t>
+          <t>90401421000</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -26930,16 +26930,16 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
+          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>93519430000</t>
+          <t>93519420000</t>
         </is>
       </c>
       <c r="C644" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -26950,16 +26950,16 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
+          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>93519440000</t>
+          <t>93519430000</t>
         </is>
       </c>
       <c r="C645" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -26970,16 +26970,16 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
+          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>93519410000</t>
+          <t>93519440000</t>
         </is>
       </c>
       <c r="C646" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -26990,16 +26990,16 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
+          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>93519460000</t>
+          <t>93519410000</t>
         </is>
       </c>
       <c r="C647" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -27010,16 +27010,16 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
+          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>93519450000</t>
+          <t>93519460000</t>
         </is>
       </c>
       <c r="C648" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -27030,16 +27030,16 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
+          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>93519540000</t>
+          <t>93519450000</t>
         </is>
       </c>
       <c r="C649" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -27050,16 +27050,16 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>93519470000</t>
+          <t>93519540000</t>
         </is>
       </c>
       <c r="C650" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -27070,16 +27070,16 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
+          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>93519500000</t>
+          <t>93519470000</t>
         </is>
       </c>
       <c r="C651" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -27090,16 +27090,16 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
+          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>93519550000</t>
+          <t>93519500000</t>
         </is>
       </c>
       <c r="C652" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -27110,12 +27110,12 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
+          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>93519510000</t>
+          <t>93519550000</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -27130,16 +27130,16 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
+          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>93519490000</t>
+          <t>93519510000</t>
         </is>
       </c>
       <c r="C654" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -27150,16 +27150,16 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
+          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>93519530000</t>
+          <t>93519490000</t>
         </is>
       </c>
       <c r="C655" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -27170,16 +27170,16 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
+          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>93519520000</t>
+          <t>93519530000</t>
         </is>
       </c>
       <c r="C656" t="n">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -27190,16 +27190,16 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
+          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>93519480000</t>
+          <t>93519520000</t>
         </is>
       </c>
       <c r="C657" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -27210,16 +27210,16 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO CARNE POUCH 85G · 93520280000</t>
+          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>93520280000</t>
+          <t>93519480000</t>
         </is>
       </c>
       <c r="C658" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -27230,16 +27230,16 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO RZ MD 13KG · 93520220000</t>
+          <t>PP PROPLAN ADULTO CARNE POUCH 85G · 93520280000</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>93520220000</t>
+          <t>93520280000</t>
         </is>
       </c>
       <c r="C659" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -27250,16 +27250,16 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO SENSIBLE MD 3KG · 93520140000</t>
+          <t>PP PROPLAN ADULTO RZ MD 13KG · 93520220000</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>93520140000</t>
+          <t>93520220000</t>
         </is>
       </c>
       <c r="C660" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -27270,16 +27270,16 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>PP PROPLAN BAJO EN CALORIAS 3KG · 93520240000</t>
+          <t>PP PROPLAN ADULTO SENSIBLE MD 3KG · 93520140000</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>93520240000</t>
+          <t>93520140000</t>
         </is>
       </c>
       <c r="C661" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -27290,16 +27290,16 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ GDE 13KG · 93520210000</t>
+          <t>PP PROPLAN BAJO EN CALORIAS 3KG · 93520240000</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>93520210000</t>
+          <t>93520240000</t>
         </is>
       </c>
       <c r="C662" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -27310,12 +27310,12 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ MD 13KG · 93520200000</t>
+          <t>PP PROPLAN CACHORRO RZ GDE 13KG · 93520210000</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>93520200000</t>
+          <t>93520210000</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -27330,16 +27330,16 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ MD 7.5KG · 93520190000</t>
+          <t>PP PROPLAN CACHORRO RZ MD 13KG · 93520200000</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>93520190000</t>
+          <t>93520200000</t>
         </is>
       </c>
       <c r="C664" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -27350,16 +27350,16 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
+          <t>PP PROPLAN CACHORRO RZ MD 7.5KG · 93520190000</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>93520160000</t>
+          <t>93520190000</t>
         </is>
       </c>
       <c r="C665" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -27370,16 +27370,16 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ PQNA 7.5KG · 93520180000</t>
+          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>93520180000</t>
+          <t>93520160000</t>
         </is>
       </c>
       <c r="C666" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -27390,16 +27390,16 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS POUCH 85 G · 93520260000</t>
+          <t>PP PROPLAN CACHORRO RZ PQNA 7.5KG · 93520180000</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>93520260000</t>
+          <t>93520180000</t>
         </is>
       </c>
       <c r="C667" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -27410,16 +27410,16 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
+          <t>PP PROPLAN CACHORROS POUCH 85 G · 93520260000</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>93520130000</t>
+          <t>93520260000</t>
         </is>
       </c>
       <c r="C668" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -27430,16 +27430,16 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>PP PROPLAN GATITO POLLO/ARROZ 1.5KG · 93520250000</t>
+          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>93520250000</t>
+          <t>93520130000</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -27450,16 +27450,16 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>PP PROPLAN MENTE ACTIVA RZ MD 3KG · 93520230000</t>
+          <t>PP PROPLAN GATITO POLLO/ARROZ 1.5KG · 93520250000</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>93520230000</t>
+          <t>93520250000</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -27470,16 +27470,16 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>PP PROPLAN RZ MD Y GDE OPTIFIT 13KG · 93520150000</t>
+          <t>PP PROPLAN MENTE ACTIVA RZ MD 3KG · 93520230000</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>93520150000</t>
+          <t>93520230000</t>
         </is>
       </c>
       <c r="C671" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -27490,16 +27490,16 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>PP SENIOR  ACTIVE MIND RZ MEDIANA 13KG · 93501261000</t>
+          <t>PP PROPLAN RZ MD Y GDE OPTIFIT 13KG · 93520150000</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>93501261000</t>
+          <t>93520150000</t>
         </is>
       </c>
       <c r="C672" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -27510,16 +27510,16 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>PP SENIOR  ACTIVE MIND RZ PQNA 3KG · 93510271000</t>
+          <t>PP SENIOR  ACTIVE MIND RZ MEDIANA 13KG · 93501261000</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>93510271000</t>
+          <t>93501261000</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -27530,16 +27530,16 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PP SENIOR  ACTIVE MIND RZ PQNA 3KG · 93510271000</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>93519400000</t>
+          <t>93510271000</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -27550,12 +27550,12 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>90038410000</t>
+          <t>93519400000</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -27570,12 +27570,12 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>90038380000</t>
+          <t>90038410000</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -27590,16 +27590,16 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>90038430000</t>
+          <t>90038380000</t>
         </is>
       </c>
       <c r="C677" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -27610,16 +27610,16 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>90038400000</t>
+          <t>90038430000</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -27630,16 +27630,16 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
+          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>90038390000</t>
+          <t>90038400000</t>
         </is>
       </c>
       <c r="C679" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -27650,16 +27650,16 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
+          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>90038590000</t>
+          <t>90038390000</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -27670,16 +27670,16 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO EXIGENTE RZ PQNA 3KG · 93520060000</t>
+          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>93520060000</t>
+          <t>90038590000</t>
         </is>
       </c>
       <c r="C681" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -27690,16 +27690,16 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MD OPTIHEALTH 7.5 · 93520070000</t>
+          <t>PROPLAN ADULTO EXIGENTE RZ PQNA 3KG · 93520060000</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>93520070000</t>
+          <t>93520060000</t>
         </is>
       </c>
       <c r="C682" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -27710,12 +27710,12 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
+          <t>PROPLAN ADULTO RZ MD OPTIHEALTH 7.5 · 93520070000</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>93520000000</t>
+          <t>93520070000</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -27730,16 +27730,16 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>PROPLAN EXIGENT BOCADOS PEQUENOS 1KG MX · 90038580000</t>
+          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>90038580000</t>
+          <t>93520000000</t>
         </is>
       </c>
       <c r="C684" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -27750,16 +27750,16 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>PROPLAN GATO ESTERILIZADO SALMON 3K · 93519980000</t>
+          <t>PROPLAN EXIGENT BOCADOS PEQUENOS 1KG MX · 90038580000</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>93519980000</t>
+          <t>90038580000</t>
         </is>
       </c>
       <c r="C685" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -27770,16 +27770,16 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
+          <t>PROPLAN GATO ESTERILIZADO SALMON 3K · 93519980000</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>93519990000</t>
+          <t>93519980000</t>
         </is>
       </c>
       <c r="C686" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -27790,16 +27790,16 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>PROPLAN MENTE ACTIVA BOCADOS PEQ 1KG MX · 90038610000</t>
+          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>90038610000</t>
+          <t>93519990000</t>
         </is>
       </c>
       <c r="C687" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -27810,16 +27810,16 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>PROPLAN OPTIDERMA RZ PQNA 7.5KG · 93520010000</t>
+          <t>PROPLAN MENTE ACTIVA BOCADOS PEQ 1KG MX · 90038610000</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>93520010000</t>
+          <t>90038610000</t>
         </is>
       </c>
       <c r="C688" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -27830,16 +27830,16 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>PROPLAN PIEL SENSI ADULTO RAZAS PEQ 1KG · 90038600000</t>
+          <t>PROPLAN OPTIDERMA RZ PQNA 7.5KG · 93520010000</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>90038600000</t>
+          <t>93520010000</t>
         </is>
       </c>
       <c r="C689" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -27850,16 +27850,16 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
+          <t>PROPLAN PIEL SENSI ADULTO RAZAS PEQ 1KG · 90038600000</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>90038570000</t>
+          <t>90038600000</t>
         </is>
       </c>
       <c r="C690" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -27870,16 +27870,16 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
+          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>93519970000</t>
+          <t>90038570000</t>
         </is>
       </c>
       <c r="C691" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -27890,36 +27890,36 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>D PC MEZCLA P/HELADO SABOR MMANI 2 · 93519010000</t>
+          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>93519010000</t>
+          <t>93519970000</t>
         </is>
       </c>
       <c r="C692" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>PUPPY CAKE</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>D PC MEZCLA P/PASTEL SABOR BANANA · 93518830000</t>
+          <t>D PC MEZCLA P/HELADO SABOR MMANI 2 · 93519010000</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>93518830000</t>
+          <t>93519010000</t>
         </is>
       </c>
       <c r="C693" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -27930,16 +27930,16 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>PC KIT P/PASTEL CUMPLEANOS CALABAZA · 93518920000</t>
+          <t>D PC MEZCLA P/PASTEL SABOR BANANA · 93518830000</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>93518920000</t>
+          <t>93518830000</t>
         </is>
       </c>
       <c r="C694" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -27950,16 +27950,16 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>PC KIT P/PASTEL D CUMPLEANOS M MANNÂ · 93518900000</t>
+          <t>PC KIT P/PASTEL CUMPLEANOS CALABAZA · 93518920000</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>93518900000</t>
+          <t>93518920000</t>
         </is>
       </c>
       <c r="C695" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -27970,16 +27970,16 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>PC KIT PARA PASTEL DE CUMPLEANOS · 93518860000</t>
+          <t>PC KIT P/PASTEL D CUMPLEANOS M MANNÂ · 93518900000</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>93518860000</t>
+          <t>93518900000</t>
         </is>
       </c>
       <c r="C696" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -27990,12 +27990,12 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>PC KIT PASTEL DE CUMPLEANOS/BANANA · 93518840000</t>
+          <t>PC KIT PARA PASTEL DE CUMPLEANOS · 93518860000</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>93518840000</t>
+          <t>93518860000</t>
         </is>
       </c>
       <c r="C697" t="n">
@@ -28010,16 +28010,16 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>PC MEZCLA P/PASTEL CUMPLEANOS CALAB · 93518910000</t>
+          <t>PC KIT PASTEL DE CUMPLEANOS/BANANA · 93518840000</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>93518910000</t>
+          <t>93518840000</t>
         </is>
       </c>
       <c r="C698" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -28030,16 +28030,16 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>PC MEZCLA P/PASTEL CUMPLEANOS MMANN? · 93518890000</t>
+          <t>PC MEZCLA P/PASTEL CUMPLEANOS CALAB · 93518910000</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>93518890000</t>
+          <t>93518910000</t>
         </is>
       </c>
       <c r="C699" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -28050,16 +28050,16 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>PC MEZCLA PARA PASTEL DE CUMPLEANOS · 93518850000</t>
+          <t>PC MEZCLA P/PASTEL CUMPLEANOS MMANN? · 93518890000</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>93518850000</t>
+          <t>93518890000</t>
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -28070,36 +28070,36 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
+          <t>PC MEZCLA PARA PASTEL DE CUMPLEANOS · 93518850000</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>90040920000</t>
+          <t>93518850000</t>
         </is>
       </c>
       <c r="C701" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>PUPPY CAKE</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
+          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>90040930000</t>
+          <t>90040920000</t>
         </is>
       </c>
       <c r="C702" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -28110,16 +28110,16 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
+          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>93520020000</t>
+          <t>90040930000</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -28130,16 +28130,16 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>PRO PLAN ADULTO RAZA PEQUEÑA 4x3.5kgMX · 90026960000</t>
+          <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>90026960000</t>
+          <t>93520020000</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -28150,16 +28150,16 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
+          <t>PRO PLAN ADULTO RAZA PEQUEÑA 4x3.5kgMX · 90026960000</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>90026950000</t>
+          <t>90026960000</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -28170,16 +28170,16 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
+          <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>93516230000</t>
+          <t>90026950000</t>
         </is>
       </c>
       <c r="C706" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -28190,16 +28190,16 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
+          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>93516200000</t>
+          <t>93516230000</t>
         </is>
       </c>
       <c r="C707" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -28210,16 +28210,16 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
+          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>93516210000</t>
+          <t>93516200000</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -28230,16 +28230,16 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>PURINA FELIX SALMON EN SALSA 85G · 93516220000</t>
+          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>93516220000</t>
+          <t>93516210000</t>
         </is>
       </c>
       <c r="C709" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -28250,16 +28250,16 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>SNACK BEGGIN STRIPS BACON 85G · 90401200000</t>
+          <t>PURINA FELIX SALMON EN SALSA 85G · 93516220000</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>90401200000</t>
+          <t>93516220000</t>
         </is>
       </c>
       <c r="C710" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -28270,36 +28270,36 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>D RB  HUESO PQNO RELLENO M MANNÂ · 93512200000</t>
+          <t>SNACK BEGGIN STRIPS BACON 85G · 90401200000</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>93512200000</t>
+          <t>90401200000</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>D RB CASCO DE RES RELLENO D M MANI · 93512080000</t>
+          <t>D RB  HUESO PQNO RELLENO M MANNÂ · 93512200000</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>93512080000</t>
+          <t>93512200000</t>
         </is>
       </c>
       <c r="C712" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -28310,16 +28310,16 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>D RB CUERNO DE RES RELLENO DE CARNE · 93512120000</t>
+          <t>D RB CASCO DE RES RELLENO D M MANI · 93512080000</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>93512120000</t>
+          <t>93512080000</t>
         </is>
       </c>
       <c r="C713" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -28330,16 +28330,16 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>D RB HUESO LARGO RELLENO D CARNE · 93512150000</t>
+          <t>D RB CUERNO DE RES RELLENO DE CARNE · 93512120000</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>93512150000</t>
+          <t>93512120000</t>
         </is>
       </c>
       <c r="C714" t="n">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -28350,16 +28350,16 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>D RB HUESO LARGO RELLENO D POLLO · 93512170000</t>
+          <t>D RB HUESO LARGO RELLENO D CARNE · 93512150000</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>93512170000</t>
+          <t>93512150000</t>
         </is>
       </c>
       <c r="C715" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -28370,16 +28370,16 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>D RB HUESO LARGO RELLENO M MANI · 93512190000</t>
+          <t>D RB HUESO LARGO RELLENO D POLLO · 93512170000</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>93512190000</t>
+          <t>93512170000</t>
         </is>
       </c>
       <c r="C716" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -28390,16 +28390,16 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>D RB HUESO LARGO RELLENO QUESO/TOCINO · 93512130000</t>
+          <t>D RB HUESO LARGO RELLENO M MANI · 93512190000</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>93512130000</t>
+          <t>93512190000</t>
         </is>
       </c>
       <c r="C717" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -28410,16 +28410,16 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE CARNE · 93512160000</t>
+          <t>D RB HUESO LARGO RELLENO QUESO/TOCINO · 93512130000</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>93512160000</t>
+          <t>93512130000</t>
         </is>
       </c>
       <c r="C718" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -28430,16 +28430,16 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>D RB HUESO PQNO RELLENO DE CARNE · 93512160000</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>93512180000</t>
+          <t>93512160000</t>
         </is>
       </c>
       <c r="C719" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -28450,16 +28450,16 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO QUESO/TOCINO · 93512140000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>93512140000</t>
+          <t>93512180000</t>
         </is>
       </c>
       <c r="C720" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>D RB ROSQUILLA RELLENA DE M MANI · 93512060000</t>
+          <t>D RB HUESO PQNO RELLENO QUESO/TOCINO · 93512140000</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>93512060000</t>
+          <t>93512140000</t>
         </is>
       </c>
       <c r="C721" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -28490,36 +28490,36 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>BHN CHIHUAHUA PUPPY 1.5KG · 90413690000</t>
+          <t>D RB ROSQUILLA RELLENA DE M MANI · 93512060000</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>90413690000</t>
+          <t>93512060000</t>
         </is>
       </c>
       <c r="C722" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>ROYAL CANIN</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>FCN URINARY CARE 2KG · 90413901000</t>
+          <t>BHN CHIHUAHUA PUPPY 1.5KG · 90413690000</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>90413901000</t>
+          <t>90413690000</t>
         </is>
       </c>
       <c r="C723" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -28530,16 +28530,16 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>FHN BABY CAT 400GR · 90413910100</t>
+          <t>FCN URINARY CARE 2KG · 90413901000</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>90413910100</t>
+          <t>90413901000</t>
         </is>
       </c>
       <c r="C724" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -28550,16 +28550,16 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>FHN HAIRBALL CARE 400GR · 90413930100</t>
+          <t>FHN BABY CAT 400GR · 90413910100</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>90413930100</t>
+          <t>90413910100</t>
         </is>
       </c>
       <c r="C725" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -28570,16 +28570,16 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>FHN STERILISED 2KG · 90414280000</t>
+          <t>FHN HAIRBALL CARE 400GR · 90413930100</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>90414280000</t>
+          <t>90413930100</t>
         </is>
       </c>
       <c r="C726" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -28590,16 +28590,16 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>ROYAL CAN BHN SHITZU ADULTO 1.5 KG. · 90401980000</t>
+          <t>FHN STERILISED 2KG · 90414280000</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>90401980000</t>
+          <t>90414280000</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -28610,16 +28610,16 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>ROYAL CANI ADULTO YORKSHIRE 1.5 KG. · 90401970000</t>
+          <t>ROYAL CAN BHN SHITZU ADULTO 1.5 KG. · 90401980000</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>90401970000</t>
+          <t>90401980000</t>
         </is>
       </c>
       <c r="C728" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -28630,12 +28630,12 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>ROYAL CANIN  FELINE FIT32-2 KG · 90401390000</t>
+          <t>ROYAL CANI ADULTO YORKSHIRE 1.5 KG. · 90401970000</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>90401390000</t>
+          <t>90401970000</t>
         </is>
       </c>
       <c r="C729" t="n">
@@ -28650,16 +28650,16 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>ROYAL CANIN  MAXI PUPPY 4 KG. · 90401720000</t>
+          <t>ROYAL CANIN  FELINE FIT32-2 KG · 90401390000</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>90401720000</t>
+          <t>90401390000</t>
         </is>
       </c>
       <c r="C730" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -28670,16 +28670,16 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ADULT POODLE 1.5KG · 90401950000</t>
+          <t>ROYAL CANIN  MAXI PUPPY 4 KG. · 90401720000</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>90401950000</t>
+          <t>90401720000</t>
         </is>
       </c>
       <c r="C731" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -28690,16 +28690,16 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIM. BABY CAT 2 KG · 90404370000</t>
+          <t>ROYAL CANIN ADULT POODLE 1.5KG · 90401950000</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>90404370000</t>
+          <t>90401950000</t>
         </is>
       </c>
       <c r="C732" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -28710,16 +28710,16 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIM. KITTEN 36 -2 KG · 90401430000</t>
+          <t>ROYAL CANIN ALIM. BABY CAT 2 KG · 90404370000</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>90401430000</t>
+          <t>90404370000</t>
         </is>
       </c>
       <c r="C733" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -28730,16 +28730,16 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIM. P GATITOS 400GR · 90404300000</t>
+          <t>ROYAL CANIN ALIM. KITTEN 36 -2 KG · 90401430000</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>90404300000</t>
+          <t>90401430000</t>
         </is>
       </c>
       <c r="C734" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -28750,16 +28750,16 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIMENTO P/COCKER 3KG · 90409490000</t>
+          <t>ROYAL CANIN ALIM. P GATITOS 400GR · 90404300000</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>90409490000</t>
+          <t>90404300000</t>
         </is>
       </c>
       <c r="C735" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -28770,16 +28770,16 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
+          <t>ROYAL CANIN ALIMENTO P/COCKER 3KG · 90409490000</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>90412110000</t>
+          <t>90409490000</t>
         </is>
       </c>
       <c r="C736" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -28790,16 +28790,16 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>ROYAL CANIN BHN SCHNAUZER 3KG · 90412080000</t>
+          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>90412080000</t>
+          <t>90412110000</t>
         </is>
       </c>
       <c r="C737" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -28810,16 +28810,16 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>ROYAL CANIN CARDIAC 2KG · 93504700000</t>
+          <t>ROYAL CANIN BHN SCHNAUZER 3KG · 90412080000</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>93504700000</t>
+          <t>90412080000</t>
         </is>
       </c>
       <c r="C738" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -28830,16 +28830,16 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>ROYAL CANIN DERMA CONFORT 3KG · 93515360000</t>
+          <t>ROYAL CANIN CARDIAC 2KG · 93504700000</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>93515360000</t>
+          <t>93504700000</t>
         </is>
       </c>
       <c r="C739" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -28850,16 +28850,16 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
+          <t>ROYAL CANIN DERMA CONFORT 3KG · 93515360000</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>93505490000</t>
+          <t>93515360000</t>
         </is>
       </c>
       <c r="C740" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -28870,16 +28870,16 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO 7.5KG · 93505500000</t>
+          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>93505500000</t>
+          <t>93505490000</t>
         </is>
       </c>
       <c r="C741" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -28890,16 +28890,16 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
+          <t>ROYAL CANIN GASTRO 7.5KG · 93505500000</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>90006770000</t>
+          <t>93505500000</t>
         </is>
       </c>
       <c r="C742" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -28910,12 +28910,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
+          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>93505710000</t>
+          <t>90006770000</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -28930,16 +28930,16 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO PERSA 2KG · 90410060000</t>
+          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>90410060000</t>
+          <t>93505710000</t>
         </is>
       </c>
       <c r="C744" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -28950,16 +28950,16 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
+          <t>ROYAL CANIN GATO PERSA 2KG · 90410060000</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>93505700000</t>
+          <t>90410060000</t>
         </is>
       </c>
       <c r="C745" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -28970,16 +28970,16 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
+          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>93505510000</t>
+          <t>93505700000</t>
         </is>
       </c>
       <c r="C746" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -28990,16 +28990,16 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
+          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>90006780000</t>
+          <t>93505510000</t>
         </is>
       </c>
       <c r="C747" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -29010,16 +29010,16 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>ROYAL CANIN INDOOR 27 2 KG · 90404330000</t>
+          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>90404330000</t>
+          <t>90006780000</t>
         </is>
       </c>
       <c r="C748" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -29030,16 +29030,16 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>ROYAL CANIN INTENSE HAIRBALL 2 KG · 90407150000</t>
+          <t>ROYAL CANIN INDOOR 27 2 KG · 90404330000</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>90407150000</t>
+          <t>90404330000</t>
         </is>
       </c>
       <c r="C749" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -29050,16 +29050,16 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MAXI ADULTO 15KG. · 90401790000</t>
+          <t>ROYAL CANIN INTENSE HAIRBALL 2 KG · 90407150000</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>90401790000</t>
+          <t>90407150000</t>
         </is>
       </c>
       <c r="C750" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -29070,16 +29070,16 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MAXI ADULTO 4 KG · 90401750000</t>
+          <t>ROYAL CANIN MAXI ADULTO 15KG. · 90401790000</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>90401750000</t>
+          <t>90401790000</t>
         </is>
       </c>
       <c r="C751" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -29090,16 +29090,16 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MAXI PUPPY 1 KG · 90401700000</t>
+          <t>ROYAL CANIN MAXI ADULTO 4 KG · 90401750000</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>90401700000</t>
+          <t>90401750000</t>
         </is>
       </c>
       <c r="C752" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -29110,16 +29110,16 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MAXI PUPPY 15 KG · 90401740000</t>
+          <t>ROYAL CANIN MAXI PUPPY 1 KG · 90401700000</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>90401740000</t>
+          <t>90401700000</t>
         </is>
       </c>
       <c r="C753" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -29130,16 +29130,16 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MEDIUM ADULTO 4KG · 90401570000</t>
+          <t>ROYAL CANIN MAXI PUPPY 15 KG · 90401740000</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>90401570000</t>
+          <t>90401740000</t>
         </is>
       </c>
       <c r="C754" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -29150,16 +29150,16 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MEDIUM PUPPY 1 KG · 90405320000</t>
+          <t>ROYAL CANIN MEDIUM ADULTO 4KG · 90401570000</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>90405320000</t>
+          <t>90401570000</t>
         </is>
       </c>
       <c r="C755" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -29170,16 +29170,16 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MINI ADULT 8+ 2KG · 90401530000</t>
+          <t>ROYAL CANIN MEDIUM PUPPY 1 KG · 90405320000</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>90401530000</t>
+          <t>90405320000</t>
         </is>
       </c>
       <c r="C756" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -29190,16 +29190,16 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MINI ADULTO 2 KG. · 90401490000</t>
+          <t>ROYAL CANIN MINI ADULT 8+ 2KG · 90401530000</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>90401490000</t>
+          <t>90401530000</t>
         </is>
       </c>
       <c r="C757" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -29210,16 +29210,16 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MINI ADULTO 800GR · 90006740000</t>
+          <t>ROYAL CANIN MINI ADULTO 2 KG. · 90401490000</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>90006740000</t>
+          <t>90401490000</t>
         </is>
       </c>
       <c r="C758" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -29230,16 +29230,16 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MINI LIGHT WEIGHTCARE 3 · 93515370000</t>
+          <t>ROYAL CANIN MINI ADULTO 800GR · 90006740000</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>93515370000</t>
+          <t>90006740000</t>
         </is>
       </c>
       <c r="C759" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -29250,16 +29250,16 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>ROYAL CANIN RENAL 2KG · 93510310000</t>
+          <t>ROYAL CANIN MINI LIGHT WEIGHTCARE 3 · 93515370000</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>93510310000</t>
+          <t>93515370000</t>
         </is>
       </c>
       <c r="C760" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -29270,16 +29270,16 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
+          <t>ROYAL CANIN RENAL 2KG · 93510310000</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>90006790000</t>
+          <t>93510310000</t>
         </is>
       </c>
       <c r="C761" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -29290,16 +29290,16 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MAXI ADULT 10K · 90412070000</t>
+          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>90412070000</t>
+          <t>90006790000</t>
         </is>
       </c>
       <c r="C762" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -29310,16 +29310,16 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI ADULTO 4KG · 90409890000</t>
+          <t>ROYAL CANIN SHN MAXI ADULT 10K · 90412070000</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>90409890000</t>
+          <t>90412070000</t>
         </is>
       </c>
       <c r="C763" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -29330,16 +29330,16 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
+          <t>ROYAL CANIN SHN MINI ADULTO 4KG · 90409890000</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>90404120000</t>
+          <t>90409890000</t>
         </is>
       </c>
       <c r="C764" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -29350,16 +29350,16 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI PUPPY 4K · 90404060000</t>
+          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>90404060000</t>
+          <t>90404120000</t>
         </is>
       </c>
       <c r="C765" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -29370,16 +29370,16 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
+          <t>ROYAL CANIN SHN MINI PUPPY 4K · 90404060000</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>93505570000</t>
+          <t>90404060000</t>
         </is>
       </c>
       <c r="C766" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -29390,16 +29390,16 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>ROYAL CANIN XSMALL ADULTO 1.5 KG · 90006750000</t>
+          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>90006750000</t>
+          <t>93505570000</t>
         </is>
       </c>
       <c r="C767" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -29410,16 +29410,16 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>ROYAL CANIN XSMALL PUPPY 1.5KG · 90006760000</t>
+          <t>ROYAL CANIN XSMALL ADULTO 1.5 KG · 90006750000</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>90006760000</t>
+          <t>90006750000</t>
         </is>
       </c>
       <c r="C768" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -29430,16 +29430,16 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
+          <t>ROYAL CANIN XSMALL PUPPY 1.5KG · 90006760000</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>90407030000</t>
+          <t>90006760000</t>
         </is>
       </c>
       <c r="C769" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -29450,16 +29450,16 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>ROYALCANIN HIPOALERGENICO 7KG · 90407040000</t>
+          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>90407040000</t>
+          <t>90407030000</t>
         </is>
       </c>
       <c r="C770" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -29470,12 +29470,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>ROYALCANIN SATIETY 1.5KG · 93516260000</t>
+          <t>ROYALCANIN HIPOALERGENICO 7KG · 90407040000</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>93516260000</t>
+          <t>90407040000</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -29490,16 +29490,16 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>SHN MINI PUPPY 800GR · 90414290000</t>
+          <t>ROYALCANIN SATIETY 1.5KG · 93516260000</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>90414290000</t>
+          <t>93516260000</t>
         </is>
       </c>
       <c r="C772" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -29510,16 +29510,16 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
+          <t>SHN MINI PUPPY 800GR · 90414290000</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>90414301000</t>
+          <t>90414290000</t>
         </is>
       </c>
       <c r="C773" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -29530,16 +29530,16 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>VHN GASTRO INT FELINO 2KG · 90414501000</t>
+          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>90414501000</t>
+          <t>90414301000</t>
         </is>
       </c>
       <c r="C774" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -29550,20 +29550,20 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA DE HIGADO 1 · 93513070000</t>
+          <t>VHN GASTRO INT FELINO 2KG · 90414501000</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>93513070000</t>
+          <t>90414501000</t>
         </is>
       </c>
       <c r="C775" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>ROYAL CANIN</t>
         </is>
       </c>
     </row>
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         </is>
       </c>
       <c r="C798" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         </is>
       </c>
       <c r="C800" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         </is>
       </c>
       <c r="C805" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         </is>
       </c>
       <c r="C807" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         </is>
       </c>
       <c r="C809" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         </is>
       </c>
       <c r="C812" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         </is>
       </c>
       <c r="C816" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         </is>
       </c>
       <c r="C822" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         </is>
       </c>
       <c r="C828" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         </is>
       </c>
       <c r="C832" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         </is>
       </c>
       <c r="C840" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         </is>
       </c>
       <c r="C841" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         </is>
       </c>
       <c r="C842" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         </is>
       </c>
       <c r="C843" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         </is>
       </c>
       <c r="C853" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         </is>
       </c>
       <c r="C855" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         </is>
       </c>
       <c r="C865" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         </is>
       </c>
       <c r="C867" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         </is>
       </c>
       <c r="C871" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         </is>
       </c>
       <c r="C874" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         </is>
       </c>
       <c r="C875" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         </is>
       </c>
       <c r="C889" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         </is>
       </c>
       <c r="C899" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         </is>
       </c>
       <c r="C908" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
     </row>
